--- a/questionnaire_templates/027_cryptography_knowledge_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/027_cryptography_knowledge_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>What is cryptography?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_cryptography</t>
+          <t>Types of cryptography</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_is_cryptography</t>
+          <t>Key Exchange methods</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>key_exchange</t>
+          <t>What is a key?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>key_exchange</t>
+          <t>Methods of Key Management</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>key_exchange</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>key_exchange</t>
+          <t>Types of symmetric key encryption</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>encryption</t>
+          <t>What is encryption?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>key_management</t>
+          <t>Methods of asymmetric key encryption</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>key_Exchange</t>
+          <t>Key Exchange methods in real-world scenarios</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>key_exchange</t>
+          <t>Question 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>encryption</t>
+          <t>What is a private key?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,90 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>key_management</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>key_management</t>
+          <t>Methods of Key Management in real-world scenarios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>key_Exchange</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_11</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>key_exchange</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>key_Exchange</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,51 +827,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>symmetric_key_exchange</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>symmetric key exchange</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>asymmetric_key_exchange</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>asymmetric key exchange</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>hashing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>hashing</t>
         </is>
       </c>
     </row>
@@ -952,352 +883,284 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>public_key_exchange</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>public key exchange</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>private_key_exchange</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>private key exchange</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>diffie-hellman</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Diffie-Hellman</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>public_key_management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>public key management</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>key_warehouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>key warehouse</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>key_escrow</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>key escrow</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>aes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>AES</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>des</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>DES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>block_cipher</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>block cipher</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>rsa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>RSA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>elliptic_curve</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>Elliptic Curve</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>ssl</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>SSL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tls</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TLS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>block_cipher</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>block cipher</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>stream_cipher</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>stream cipher</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>hsm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>HSM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>key_management_server</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option18</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Key Management Server</t>
         </is>
       </c>
     </row>
